--- a/exploratory_data_analysis/dimensions_reduction/risultati/statistiche_descrittive.xlsx
+++ b/exploratory_data_analysis/dimensions_reduction/risultati/statistiche_descrittive.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>gdp-pop-urban_merged</t>
+          <t>gdp_pop_urban_merged</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         <v>41.5145742480835</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-2.077610338479825e-17</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         <v>15.56122696349549</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3581700869467754</v>
+        <v>-0.3581700869467753</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         <v>34.20183389023812</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.344051027435393</v>
+        <v>-0.3440510274353928</v>
       </c>
     </row>
     <row r="8">
@@ -889,7 +889,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="n">
-        <v>26.14180082354963</v>
+        <v>26.14180082354962</v>
       </c>
     </row>
   </sheetData>
